--- a/artfynd/A 44439-2023 artfynd.xlsx
+++ b/artfynd/A 44439-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73695403</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445027.217388843</v>
+        <v>445027</v>
       </c>
       <c r="R2" t="n">
-        <v>6432015.740428224</v>
+        <v>6432016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73695405</v>
+        <v>73695404</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445454.0740192892</v>
+        <v>445386</v>
       </c>
       <c r="R3" t="n">
-        <v>6432069.202908561</v>
+        <v>6432061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +865,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73695404</v>
+        <v>73695405</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445386.039124348</v>
+        <v>445454</v>
       </c>
       <c r="R4" t="n">
-        <v>6432061.129614111</v>
+        <v>6432069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,19 +977,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44439-2023 artfynd.xlsx
+++ b/artfynd/A 44439-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,8 +1023,18 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>